--- a/PAMF_DIG F2 - monthly2026-07-16.xlsx
+++ b/PAMF_DIG F2 - monthly2026-07-16.xlsx
@@ -4429,7 +4429,7 @@
         <v>0.09</v>
       </c>
       <c r="N55" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -9758,7 +9758,7 @@
         <v>0.09</v>
       </c>
       <c r="N128" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         <v>0.09</v>
       </c>
       <c r="N155" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O155" t="inlineStr">
         <is>
@@ -17058,7 +17058,7 @@
         <v>0.09</v>
       </c>
       <c r="N228" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O228" t="inlineStr">
         <is>
@@ -19613,7 +19613,7 @@
         <v>0.09</v>
       </c>
       <c r="N263" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O263" t="inlineStr">
         <is>

--- a/PAMF_DIG F2 - monthly2026-07-16.xlsx
+++ b/PAMF_DIG F2 - monthly2026-07-16.xlsx
@@ -3261,7 +3261,7 @@
         <v>0.09</v>
       </c>
       <c r="N39" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>0.09</v>
       </c>
       <c r="N57" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>0.09</v>
       </c>
       <c r="N199" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O199" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
         <v>0.09</v>
       </c>
       <c r="N200" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O200" t="inlineStr">
         <is>
@@ -17642,7 +17642,7 @@
         <v>0.09</v>
       </c>
       <c r="N236" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O236" t="inlineStr">
         <is>
@@ -18226,7 +18226,7 @@
         <v>0.09</v>
       </c>
       <c r="N244" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O244" t="inlineStr">
         <is>
@@ -20343,7 +20343,7 @@
         <v>0.09</v>
       </c>
       <c r="N273" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O273" t="inlineStr">
         <is>
